--- a/data/weights/AA-LIVE HYDRATED BODY WEIGHT DATA-1995-2016/BODY WEIGHTS-2009-Kens 15 Sets.xlsx
+++ b/data/weights/AA-LIVE HYDRATED BODY WEIGHT DATA-1995-2016/BODY WEIGHTS-2009-Kens 15 Sets.xlsx
@@ -1,10 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <fileVersion appName="xl" lastEdited="4" lowestEdited="4" rupBuild="4507"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="10927"/>
   <workbookPr defaultThemeVersion="124226"/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice Requires="x15">
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/walker/Documents/Github/wind-tunnel-flies/data/weights/AA-LIVE HYDRATED BODY WEIGHT DATA-1995-2016/"/>
+    </mc:Choice>
+  </mc:AlternateContent>
+  <xr:revisionPtr revIDLastSave="0" documentId="11_A7598456F57F2949F641E4ADB9C0C07E9DD84C44" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="60" windowWidth="18195" windowHeight="10005" firstSheet="8" activeTab="16"/>
+    <workbookView xWindow="1980" yWindow="4540" windowWidth="19220" windowHeight="12880" firstSheet="8" activeTab="16" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -25,7 +31,20 @@
     <sheet name="Sheet16" sheetId="16" r:id="rId16"/>
     <sheet name="Sheet17" sheetId="17" r:id="rId17"/>
   </sheets>
-  <calcPr calcId="125725"/>
+  <calcPr calcId="191029"/>
+  <extLst>
+    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
+      <xcalcf:calcFeatures>
+        <xcalcf:feature name="microsoft.com:RD"/>
+        <xcalcf:feature name="microsoft.com:Single"/>
+        <xcalcf:feature name="microsoft.com:FV"/>
+        <xcalcf:feature name="microsoft.com:CNMTM"/>
+        <xcalcf:feature name="microsoft.com:LET_WF"/>
+        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
+        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
+      </xcalcf:calcFeatures>
+    </ext>
+  </extLst>
 </workbook>
 </file>
 
@@ -662,8 +681,8 @@
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <fonts count="2">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
+  <fonts count="2" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -709,13 +728,21 @@
   </cellStyles>
   <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
+  <extLst>
+    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
+      <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
+    </ext>
+    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
+      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
+    </ext>
+  </extLst>
 </styleSheet>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme 2007 - 2010">
   <a:themeElements>
-    <a:clrScheme name="Office">
+    <a:clrScheme name="Office 2007 - 2010">
       <a:dk1>
         <a:sysClr val="windowText" lastClr="000000"/>
       </a:dk1>
@@ -753,7 +780,7 @@
         <a:srgbClr val="800080"/>
       </a:folHlink>
     </a:clrScheme>
-    <a:fontScheme name="Office">
+    <a:fontScheme name="Office 2007 - 2010">
       <a:majorFont>
         <a:latin typeface="Cambria"/>
         <a:ea typeface=""/>
@@ -787,6 +814,7 @@
         <a:font script="Mong" typeface="Mongolian Baiti"/>
         <a:font script="Viet" typeface="Times New Roman"/>
         <a:font script="Uigh" typeface="Microsoft Uighur"/>
+        <a:font script="Geor" typeface="Sylfaen"/>
       </a:majorFont>
       <a:minorFont>
         <a:latin typeface="Calibri"/>
@@ -821,9 +849,10 @@
         <a:font script="Mong" typeface="Mongolian Baiti"/>
         <a:font script="Viet" typeface="Arial"/>
         <a:font script="Uigh" typeface="Microsoft Uighur"/>
+        <a:font script="Geor" typeface="Sylfaen"/>
       </a:minorFont>
     </a:fontScheme>
-    <a:fmtScheme name="Office">
+    <a:fmtScheme name="Office 2007 - 2010">
       <a:fillStyleLst>
         <a:solidFill>
           <a:schemeClr val="phClr"/>
@@ -996,11 +1025,11 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:L2"/>
-  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <sheetData>
-    <row r="1" spans="1:12" s="1" customFormat="1">
+    <row r="1" spans="1:12" s="1" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -1038,7 +1067,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="2" spans="1:12">
+    <row r="2" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A2">
         <v>3.5900000000000001E-2</v>
       </c>
@@ -1083,11 +1112,11 @@
 </file>
 
 <file path=xl/worksheets/sheet10.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0900-000000000000}">
   <dimension ref="A1:L2"/>
-  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <sheetData>
-    <row r="1" spans="1:12" s="1" customFormat="1">
+    <row r="1" spans="1:12" s="1" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A1" s="1" t="s">
         <v>108</v>
       </c>
@@ -1125,7 +1154,7 @@
         <v>119</v>
       </c>
     </row>
-    <row r="2" spans="1:12">
+    <row r="2" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A2">
         <v>3.5400000000000001E-2</v>
       </c>
@@ -1169,11 +1198,11 @@
 </file>
 
 <file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0A00-000000000000}">
   <dimension ref="A1:L2"/>
-  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <sheetData>
-    <row r="1" spans="1:12" s="1" customFormat="1">
+    <row r="1" spans="1:12" s="1" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A1" s="1" t="s">
         <v>120</v>
       </c>
@@ -1211,7 +1240,7 @@
         <v>131</v>
       </c>
     </row>
-    <row r="2" spans="1:12">
+    <row r="2" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A2">
         <v>3.9100000000000003E-2</v>
       </c>
@@ -1255,11 +1284,11 @@
 </file>
 
 <file path=xl/worksheets/sheet12.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0B00-000000000000}">
   <dimension ref="A1:L2"/>
-  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <sheetData>
-    <row r="1" spans="1:12" s="1" customFormat="1">
+    <row r="1" spans="1:12" s="1" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A1" s="1" t="s">
         <v>132</v>
       </c>
@@ -1297,7 +1326,7 @@
         <v>143</v>
       </c>
     </row>
-    <row r="2" spans="1:12">
+    <row r="2" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A2">
         <v>3.8399999999999997E-2</v>
       </c>
@@ -1341,11 +1370,11 @@
 </file>
 
 <file path=xl/worksheets/sheet13.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0C00-000000000000}">
   <dimension ref="A1:L2"/>
-  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <sheetData>
-    <row r="1" spans="1:12" s="1" customFormat="1">
+    <row r="1" spans="1:12" s="1" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A1" s="1" t="s">
         <v>144</v>
       </c>
@@ -1383,7 +1412,7 @@
         <v>155</v>
       </c>
     </row>
-    <row r="2" spans="1:12">
+    <row r="2" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A2">
         <v>3.7900000000000003E-2</v>
       </c>
@@ -1427,11 +1456,11 @@
 </file>
 
 <file path=xl/worksheets/sheet14.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0D00-000000000000}">
   <dimension ref="A1:L2"/>
-  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <sheetData>
-    <row r="1" spans="1:12" s="1" customFormat="1">
+    <row r="1" spans="1:12" s="1" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A1" s="1" t="s">
         <v>156</v>
       </c>
@@ -1469,7 +1498,7 @@
         <v>167</v>
       </c>
     </row>
-    <row r="2" spans="1:12">
+    <row r="2" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A2">
         <v>3.5200000000000002E-2</v>
       </c>
@@ -1513,11 +1542,11 @@
 </file>
 
 <file path=xl/worksheets/sheet15.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0E00-000000000000}">
   <dimension ref="A1:L2"/>
-  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <sheetData>
-    <row r="1" spans="1:12" s="1" customFormat="1">
+    <row r="1" spans="1:12" s="1" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A1" s="1" t="s">
         <v>168</v>
       </c>
@@ -1555,7 +1584,7 @@
         <v>179</v>
       </c>
     </row>
-    <row r="2" spans="1:12">
+    <row r="2" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A2">
         <v>4.2700000000000002E-2</v>
       </c>
@@ -1599,11 +1628,11 @@
 </file>
 
 <file path=xl/worksheets/sheet16.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0F00-000000000000}">
   <dimension ref="A1:L16"/>
-  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <sheetData>
-    <row r="1" spans="1:12" s="1" customFormat="1">
+    <row r="1" spans="1:12" s="1" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A1" s="1" t="s">
         <v>180</v>
       </c>
@@ -1641,7 +1670,7 @@
         <v>191</v>
       </c>
     </row>
-    <row r="2" spans="1:12">
+    <row r="2" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A2">
         <v>3.5900000000000001E-2</v>
       </c>
@@ -1679,7 +1708,7 @@
         <v>1.8499999999999999E-2</v>
       </c>
     </row>
-    <row r="3" spans="1:12">
+    <row r="3" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A3">
         <v>3.8600000000000002E-2</v>
       </c>
@@ -1717,7 +1746,7 @@
         <v>1.7899999999999999E-2</v>
       </c>
     </row>
-    <row r="4" spans="1:12">
+    <row r="4" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A4">
         <v>3.73E-2</v>
       </c>
@@ -1755,7 +1784,7 @@
         <v>1.8499999999999999E-2</v>
       </c>
     </row>
-    <row r="5" spans="1:12">
+    <row r="5" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A5">
         <v>3.73E-2</v>
       </c>
@@ -1793,7 +1822,7 @@
         <v>1.83E-2</v>
       </c>
     </row>
-    <row r="6" spans="1:12">
+    <row r="6" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A6">
         <v>4.1099999999999998E-2</v>
       </c>
@@ -1831,7 +1860,7 @@
         <v>1.7399999999999999E-2</v>
       </c>
     </row>
-    <row r="7" spans="1:12">
+    <row r="7" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A7">
         <v>3.6400000000000002E-2</v>
       </c>
@@ -1869,7 +1898,7 @@
         <v>1.8599999999999998E-2</v>
       </c>
     </row>
-    <row r="8" spans="1:12">
+    <row r="8" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A8">
         <v>2.4500000000000001E-2</v>
       </c>
@@ -1907,7 +1936,7 @@
         <v>1.7100000000000001E-2</v>
       </c>
     </row>
-    <row r="9" spans="1:12">
+    <row r="9" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A9">
         <v>3.5900000000000001E-2</v>
       </c>
@@ -1945,7 +1974,7 @@
         <v>1.9199999999999998E-2</v>
       </c>
     </row>
-    <row r="10" spans="1:12">
+    <row r="10" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A10">
         <v>4.4999999999999998E-2</v>
       </c>
@@ -1983,7 +2012,7 @@
         <v>1.83E-2</v>
       </c>
     </row>
-    <row r="11" spans="1:12">
+    <row r="11" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A11">
         <v>3.5400000000000001E-2</v>
       </c>
@@ -2021,7 +2050,7 @@
         <v>1.83E-2</v>
       </c>
     </row>
-    <row r="12" spans="1:12">
+    <row r="12" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A12">
         <v>3.9100000000000003E-2</v>
       </c>
@@ -2059,7 +2088,7 @@
         <v>1.83E-2</v>
       </c>
     </row>
-    <row r="13" spans="1:12">
+    <row r="13" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A13">
         <v>3.8399999999999997E-2</v>
       </c>
@@ -2097,7 +2126,7 @@
         <v>1.9199999999999998E-2</v>
       </c>
     </row>
-    <row r="14" spans="1:12">
+    <row r="14" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A14">
         <v>3.7900000000000003E-2</v>
       </c>
@@ -2135,7 +2164,7 @@
         <v>1.7100000000000001E-2</v>
       </c>
     </row>
-    <row r="15" spans="1:12">
+    <row r="15" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A15">
         <v>3.5200000000000002E-2</v>
       </c>
@@ -2173,7 +2202,7 @@
         <v>1.9199999999999998E-2</v>
       </c>
     </row>
-    <row r="16" spans="1:12">
+    <row r="16" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A16">
         <v>4.2700000000000002E-2</v>
       </c>
@@ -2217,15 +2246,15 @@
 </file>
 
 <file path=xl/worksheets/sheet17.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-1000-000000000000}">
   <dimension ref="A1:M25"/>
-  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="1" max="1" width="9.85546875" style="1" customWidth="1"/>
-    <col min="10" max="10" width="9.140625" customWidth="1"/>
+    <col min="1" max="1" width="9.83203125" style="1" customWidth="1"/>
+    <col min="10" max="10" width="9.1640625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:13" s="1" customFormat="1" ht="14.25" customHeight="1">
+    <row r="1" spans="1:13" s="1" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B1" s="1" t="s">
         <v>180</v>
       </c>
@@ -2263,7 +2292,7 @@
         <v>191</v>
       </c>
     </row>
-    <row r="2" spans="1:13">
+    <row r="2" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A2" s="1" t="s">
         <v>192</v>
       </c>
@@ -2304,7 +2333,7 @@
         <v>1.8499999999999999E-2</v>
       </c>
     </row>
-    <row r="3" spans="1:13">
+    <row r="3" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A3" s="1" t="s">
         <v>193</v>
       </c>
@@ -2345,7 +2374,7 @@
         <v>1.7899999999999999E-2</v>
       </c>
     </row>
-    <row r="4" spans="1:13">
+    <row r="4" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A4" s="1" t="s">
         <v>194</v>
       </c>
@@ -2386,7 +2415,7 @@
         <v>1.8499999999999999E-2</v>
       </c>
     </row>
-    <row r="5" spans="1:13">
+    <row r="5" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>195</v>
       </c>
@@ -2427,7 +2456,7 @@
         <v>1.83E-2</v>
       </c>
     </row>
-    <row r="6" spans="1:13">
+    <row r="6" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A6" s="1" t="s">
         <v>196</v>
       </c>
@@ -2468,7 +2497,7 @@
         <v>1.7399999999999999E-2</v>
       </c>
     </row>
-    <row r="7" spans="1:13">
+    <row r="7" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A7" s="1" t="s">
         <v>197</v>
       </c>
@@ -2509,7 +2538,7 @@
         <v>1.8599999999999998E-2</v>
       </c>
     </row>
-    <row r="8" spans="1:13">
+    <row r="8" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A8" s="1" t="s">
         <v>198</v>
       </c>
@@ -2547,7 +2576,7 @@
         <v>1.7100000000000001E-2</v>
       </c>
     </row>
-    <row r="9" spans="1:13">
+    <row r="9" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A9" s="1" t="s">
         <v>199</v>
       </c>
@@ -2588,7 +2617,7 @@
         <v>1.9199999999999998E-2</v>
       </c>
     </row>
-    <row r="10" spans="1:13">
+    <row r="10" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A10" s="1" t="s">
         <v>200</v>
       </c>
@@ -2629,7 +2658,7 @@
         <v>1.83E-2</v>
       </c>
     </row>
-    <row r="11" spans="1:13">
+    <row r="11" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A11" s="1" t="s">
         <v>201</v>
       </c>
@@ -2670,7 +2699,7 @@
         <v>1.83E-2</v>
       </c>
     </row>
-    <row r="12" spans="1:13">
+    <row r="12" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A12" s="1" t="s">
         <v>202</v>
       </c>
@@ -2711,7 +2740,7 @@
         <v>1.83E-2</v>
       </c>
     </row>
-    <row r="13" spans="1:13">
+    <row r="13" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A13" s="1" t="s">
         <v>203</v>
       </c>
@@ -2752,7 +2781,7 @@
         <v>1.9199999999999998E-2</v>
       </c>
     </row>
-    <row r="14" spans="1:13">
+    <row r="14" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A14" s="1" t="s">
         <v>204</v>
       </c>
@@ -2793,7 +2822,7 @@
         <v>1.7100000000000001E-2</v>
       </c>
     </row>
-    <row r="15" spans="1:13">
+    <row r="15" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A15" s="1" t="s">
         <v>205</v>
       </c>
@@ -2834,7 +2863,7 @@
         <v>1.9199999999999998E-2</v>
       </c>
     </row>
-    <row r="16" spans="1:13">
+    <row r="16" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A16" s="1" t="s">
         <v>206</v>
       </c>
@@ -2875,7 +2904,7 @@
         <v>1.7899999999999999E-2</v>
       </c>
     </row>
-    <row r="20" spans="1:13">
+    <row r="20" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A20" s="1" t="s">
         <v>207</v>
       </c>
@@ -2928,7 +2957,7 @@
         <v>1.8253333333333337E-2</v>
       </c>
     </row>
-    <row r="24" spans="1:13">
+    <row r="24" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A24" s="1" t="s">
         <v>208</v>
       </c>
@@ -2969,7 +2998,7 @@
         <v>0.91259999999999997</v>
       </c>
     </row>
-    <row r="25" spans="1:13" ht="15.75" customHeight="1"/>
+    <row r="25" spans="1:13" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="landscape" r:id="rId1"/>
@@ -2977,11 +3006,11 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
   <dimension ref="A1:L2"/>
-  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <sheetData>
-    <row r="1" spans="1:12" s="1" customFormat="1">
+    <row r="1" spans="1:12" s="1" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A1" s="1" t="s">
         <v>12</v>
       </c>
@@ -3019,7 +3048,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="2" spans="1:12">
+    <row r="2" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A2">
         <v>3.8600000000000002E-2</v>
       </c>
@@ -3063,19 +3092,19 @@
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
   <dimension ref="A1:L2"/>
-  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="2" max="2" width="9.85546875" customWidth="1"/>
-    <col min="4" max="4" width="9.85546875" customWidth="1"/>
-    <col min="6" max="6" width="10.140625" customWidth="1"/>
-    <col min="8" max="8" width="9.85546875" customWidth="1"/>
-    <col min="10" max="10" width="9.7109375" customWidth="1"/>
-    <col min="12" max="12" width="9.85546875" customWidth="1"/>
+    <col min="2" max="2" width="9.83203125" customWidth="1"/>
+    <col min="4" max="4" width="9.83203125" customWidth="1"/>
+    <col min="6" max="6" width="10.1640625" customWidth="1"/>
+    <col min="8" max="8" width="9.83203125" customWidth="1"/>
+    <col min="10" max="10" width="9.6640625" customWidth="1"/>
+    <col min="12" max="12" width="9.83203125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:12" s="1" customFormat="1">
+    <row r="1" spans="1:12" s="1" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A1" s="1" t="s">
         <v>24</v>
       </c>
@@ -3113,7 +3142,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="2" spans="1:12">
+    <row r="2" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A2">
         <v>3.73E-2</v>
       </c>
@@ -3157,11 +3186,11 @@
 </file>
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0300-000000000000}">
   <dimension ref="A1:L2"/>
-  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <sheetData>
-    <row r="1" spans="1:12" s="1" customFormat="1">
+    <row r="1" spans="1:12" s="1" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A1" s="1" t="s">
         <v>36</v>
       </c>
@@ -3199,7 +3228,7 @@
         <v>47</v>
       </c>
     </row>
-    <row r="2" spans="1:12">
+    <row r="2" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A2">
         <v>3.73E-2</v>
       </c>
@@ -3243,11 +3272,11 @@
 </file>
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0400-000000000000}">
   <dimension ref="A1:L2"/>
-  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <sheetData>
-    <row r="1" spans="1:12" s="1" customFormat="1">
+    <row r="1" spans="1:12" s="1" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A1" s="1" t="s">
         <v>48</v>
       </c>
@@ -3285,7 +3314,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="2" spans="1:12">
+    <row r="2" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A2">
         <v>4.1099999999999998E-2</v>
       </c>
@@ -3329,11 +3358,11 @@
 </file>
 
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0500-000000000000}">
   <dimension ref="A1:L2"/>
-  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <sheetData>
-    <row r="1" spans="1:12" s="1" customFormat="1">
+    <row r="1" spans="1:12" s="1" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A1" s="1" t="s">
         <v>60</v>
       </c>
@@ -3371,7 +3400,7 @@
         <v>71</v>
       </c>
     </row>
-    <row r="2" spans="1:12">
+    <row r="2" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A2">
         <v>3.6400000000000002E-2</v>
       </c>
@@ -3415,11 +3444,11 @@
 </file>
 
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0600-000000000000}">
   <dimension ref="A1:L2"/>
-  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <sheetData>
-    <row r="1" spans="1:12" s="1" customFormat="1">
+    <row r="1" spans="1:12" s="1" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A1" s="1" t="s">
         <v>72</v>
       </c>
@@ -3457,7 +3486,7 @@
         <v>83</v>
       </c>
     </row>
-    <row r="2" spans="1:12">
+    <row r="2" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A2">
         <v>2.4500000000000001E-2</v>
       </c>
@@ -3501,11 +3530,11 @@
 </file>
 
 <file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0700-000000000000}">
   <dimension ref="A1:L2"/>
-  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <sheetData>
-    <row r="1" spans="1:12" s="1" customFormat="1">
+    <row r="1" spans="1:12" s="1" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A1" s="1" t="s">
         <v>84</v>
       </c>
@@ -3543,7 +3572,7 @@
         <v>95</v>
       </c>
     </row>
-    <row r="2" spans="1:12">
+    <row r="2" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A2">
         <v>3.5900000000000001E-2</v>
       </c>
@@ -3587,11 +3616,11 @@
 </file>
 
 <file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0800-000000000000}">
   <dimension ref="A1:L2"/>
-  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <sheetData>
-    <row r="1" spans="1:12" s="1" customFormat="1">
+    <row r="1" spans="1:12" s="1" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A1" s="1" t="s">
         <v>96</v>
       </c>
@@ -3629,7 +3658,7 @@
         <v>107</v>
       </c>
     </row>
-    <row r="2" spans="1:12">
+    <row r="2" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A2">
         <v>4.4999999999999998E-2</v>
       </c>
